--- a/reports/lists/kobo_all_20260831.xlsx
+++ b/reports/lists/kobo_all_20260831.xlsx
@@ -14,10 +14,10 @@
     <sheet name="4_巡回範囲と到達度" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_直近の申請候補'!$A$1:$I$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_直近の申請候補'!$A$1:$J$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2_全案件'!$A$1:$L$256</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3_未来（未公告）'!$A$1:$E$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4_巡回範囲と到達度'!$A$1:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4_巡回範囲と到達度'!$A$1:$D$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -554,81 +554,88 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2_全案件 ──────── 台帳の全量 255件。過去の実績も次回公告の予測に使うため残してある。</t>
+          <t xml:space="preserve">　　　　　　　　　　D列「現有資格での可否」は、統一資格D・東京都C で判定した結果。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>3_未来（未公告）── まだ公告されていないが、過去のパターンから必ず出る案件。</t>
+          <t>2_全案件 ──────── 台帳の全量 255件。過去の実績も次回公告の予測に使うため残してある。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>3_未来（未公告）── まだ公告されていないが、過去のパターンから必ず出る案件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>4_巡回範囲と到達度 ─ どこまで見ているか。見ていない領域も正直に書いた。</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>この仕事の中心</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>現在募集中のものを拾うだけなら誰でもできる。過去の発注パターンから次の公告時期を</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>現在募集中のものを拾うだけなら誰でもできる。過去の発注パターンから次の公告時期を</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>逆算し、公告前から待ち構えることに価値がある。だから3のシートが本体である。</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>注意</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>・締切は「参加表明・参加申込」と「企画提案書」の二段構えのものがある。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　本リストの締切欄には、必ず早いほう（＝関門）を入れてある。</t>
+          <t>・締切は「参加表明・参加申込」と「企画提案書」の二段構えのものがある。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>・東京都の発注予定情報は、締切が過ぎると一覧から消える。8/28は1日で68件減った。</t>
+          <t xml:space="preserve">　本リストの締切欄には、必ず早いほう（＝関門）を入れてある。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>・東京都の発注予定情報は、締切が過ぎると一覧から消える。8/28は1日で68件減った。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>・予定価格が非公開の案件は、金額で足切りしていない。</t>
         </is>
@@ -645,18 +652,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -677,30 +685,35 @@
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
+          <t>現有資格での可否</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
           <t>案件名</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>発注機関</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>予定価格</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>資格の要否</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>状態・注意</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
@@ -722,19 +735,19 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
+          <t>△ 要確認</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
           <t>令和8年度中小企業地域資源活用等促進事業 展示商談会 大分県ブースの企画・運営委託業務</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>大分県産業創造機構</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
           <t>要確認</t>
@@ -742,10 +755,15 @@
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
           <t>参加申込期限(8/26)超過・要電話確認</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>https://www.columbus.or.jp/</t>
         </is>
@@ -767,19 +785,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
+          <t>△ 要確認</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
           <t>海外ビジネス人材育成及びオンラインを活用した海外販路開拓支援事業</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>大阪産業局</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
           <t>要確認</t>
@@ -787,10 +805,15 @@
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
           <t>新規（応募可）</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>https://www.obda.or.jp/</t>
         </is>
@@ -812,19 +835,19 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>△ 要確認</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
           <t>横浜グリーンエクスポにおける賓客受入等業務委託</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>横浜市 脱炭素・GREEN×EXPO推進局</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
           <t>要確認</t>
@@ -832,10 +855,15 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
           <t>新規（応募可）</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>https://www.city.yokohama.lg.jp/business/nyusatsu/kakukukyoku/2026/itaku/green/</t>
         </is>
@@ -857,30 +885,35 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
+          <t>△ 要確認</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
           <t>【公募型プロポーザル】瀬谷駅北口駅前広場から旧上瀬谷通信施設地区における緑花による装飾および育成業務委託</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>横浜市</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
           <t>新規（要締切確認）</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>https://www.city.yokohama.lg.jp/business/nyusatsu/kakukukyoku/2026/itaku/green/midorihana.html</t>
         </is>
@@ -897,35 +930,40 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>○ 応募可（C等級で届く）</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
           <t>令和8年度都立学校・海外大学連携交流事業等運営業務委託</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>東京都 教育庁総務部契約管財課</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>非公開</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>要（東京都物品／120催事関係業務・受付等級C）</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>希望申請9/1 16時。東京都の名簿に未登載のため応募不可。開札9/17 9時40分</t>
-        </is>
-      </c>
       <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>**受付等級C＝御社の現有資格で応募可。希望申請 9/1 16時（電子調達システムから）。**都立高校生と海外大学生の英語交流事業の企画・運営、会場手配、通訳者手配。履行〜令和9年1月29日。開札9/17 9時40分。教育庁総務部契約管財課 03-5320-6725</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>https://www.e-procurement.metro.tokyo.lg.jp/</t>
         </is>
@@ -947,30 +985,35 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
+          <t>× 等級不足（都はC）</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
           <t>令和8年度「東京ベイeSGパートナー」出展ブース設営等業務委託（エコプロ）</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>東京都 スタートアップ戦略推進本部戦略推進部戦略企画課</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>非公開</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>要（東京都物品／120催事関係業務・受付等級B）</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>希望申請9/2 17時。東京都の競争入札参加有資格者名簿に未登載のため応募不可。開札9/16 9時35分</t>
-        </is>
-      </c>
       <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>**受付等級B。御社はC等級のため応募できない。**希望申請9/2 17時。エコプロ2026の東京都ブース準備・運営。スタートアップ戦略推進本部</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>https://www.e-procurement.metro.tokyo.lg.jp/</t>
         </is>
@@ -992,30 +1035,35 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>× 等級不足（都はC）</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
           <t>令和8年度伝統と最先端テクノロジーが融合したモビリティのイベント運営業務委託（その3）</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>東京都 スタートアップ戦略推進本部戦略推進部戦略企画課</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>非公開</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>要（東京都物品／120催事関係業務・受付等級B）</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>希望申請9/2 17時。東京都の名簿に未登載のため応募不可。開札9/16 9時35分</t>
-        </is>
-      </c>
       <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>**受付等級B。御社はC等級のため応募できない。**希望申請9/2 17時</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>https://www.e-procurement.metro.tokyo.lg.jp/</t>
         </is>
@@ -1037,30 +1085,35 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
+          <t>△ 要確認</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
           <t>公募型プロポーザル方式「第13回“日本の食品”輸出EXPO WINTER」徳島県ブース装飾設置運営委託事業者募集に係る質問への回答について</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>徳島県</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>非公開</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
           <t>新規（応募可・参加申込9/3必着）</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>https://www.pref.tokushima.lg.jp/jigyoshanokata/nyusatsu/itaku/7315873/</t>
         </is>
@@ -1082,30 +1135,35 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>× 等級不足（都はC）</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
           <t>「女性活躍推進に向けたイベント」運営等業務委託</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>東京都</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>非公開</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>要（東京都物品／120催事関係業務・受付等級B）</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>希望申請9/3 17時。東京都の名簿に未登載のため応募不可</t>
-        </is>
-      </c>
       <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>**受付等級B。御社はC等級のため応募できない。**希望申請9/3 17時</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>https://www.e-procurement.metro.tokyo.lg.jp/</t>
         </is>
@@ -1122,35 +1180,40 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
+          <t>○ 応募可（C等級で届く）</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
           <t>「Tokyo DX/AX Connect Day 2026」運営等業務委託</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>東京都</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>非公開</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>要（東京都物品／120催事関係業務・受付等級B,C）</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>希望申請9/3 16時。**スクリプトの1ページ目問題を修正して初めて見えた案件。**名簿未登載のため応募不可</t>
-        </is>
-      </c>
       <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>**受付等級B,C＝御社の現有資格で応募可。希望申請 9/3 16時。**イベント前日の設営と当日の運営。履行〜令和9年1月29日。開札9/28 10時。デジタルサービス局総務部企画計理課 03-5388-2085</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>https://www.e-procurement.metro.tokyo.lg.jp/</t>
         </is>
@@ -1172,30 +1235,35 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
+          <t>○ 応募可（資格不要）</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
           <t>2027国際園芸博覧会への福島県出展業務委託</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>福島県</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>新規（応募可・参加申込9/4正午必着）</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>https://www.pref.fukushima.lg.jp/sec/36035c/2027engeihaku-kohbo.html</t>
         </is>
@@ -1204,56 +1272,61 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>令和8・9年度スタートアップエコシステムのプロモーション業務委託</t>
+          <t>○ 応募可（資格不要）</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>主催者催事「おまつり歳時記プロジェクト（仮）」実施計画作成業務委託</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>非公開</t>
+          <t>公益社団法人2027年国際園芸博覧会協会</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>要（東京都物品／115広告代理・受付等級A）</t>
+          <t>1,430万円（上限・税込）／後続運営は1.1〜4億円想定</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>希望申請9/4 16時。2か年契約。名簿未登載のため応募不可</t>
+          <t>不要（実績要件アで充足見込み）</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>https://www.e-procurement.metro.tokyo.lg.jp/</t>
+          <t>新規（応募可・参加意向申出9/7 17時／提案書9/29）</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>https://expo2027yokohama.or.jp/contract/detail/20260827-001348.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
@@ -1262,32 +1335,37 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>主催者催事「おまつり歳時記プロジェクト（仮）」実施計画作成業務委託</t>
+          <t>△ 要確認</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>公益社団法人2027年国際園芸博覧会協会</t>
+          <t>集団出展ブース装飾委託業務【LIFE×DESIGN 2027】</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>1,430万円（上限・税込）／後続運営は1.1〜4億円想定</t>
+          <t>公益財団法人わかやま産業振興財団</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>不要（実績要件アで充足見込み）</t>
+          <t>2,500,000円（上限・税込）</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>新規（応募可・参加意向申出9/7 17時／提案書9/29）</t>
+          <t>要（和歌山県 役務の提供等の入札参加資格）</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>https://expo2027yokohama.or.jp/contract/detail/20260827-001348.html</t>
+          <t>新規（応募可・参加申込9/8 17時必着／提案書9/29）</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>https://yarukiouendan.or.jp/news/lifedesign_soushoku_2027/</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1385,37 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>集団出展ブース装飾委託業務【LIFE×DESIGN 2027】</t>
+          <t>△ 統一資格の等級を要確認</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>公益財団法人わかやま産業振興財団</t>
+          <t>「2027年ベオグラード国際博覧会」日本館 運営</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>2,500,000円（上限・税込）</t>
+          <t>JETRO（日本貿易振興機構）</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>要（和歌山県 役務の提供等の入札参加資格）</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>新規（応募可・参加申込9/8 17時必着／提案書9/29）</t>
+          <t>要（全省庁統一資格・役務の提供等）</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>https://yarukiouendan.or.jp/news/lifedesign_soushoku_2027/</t>
+          <t>新規【募集中】</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>https://www.jetro.go.jp/procurement/bid/ode/b086abd8177ce6da.html</t>
         </is>
       </c>
     </row>
@@ -1352,122 +1435,137 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>「2027年ベオグラード国際博覧会」日本館 運営</t>
+          <t>△ 統一資格の等級を要確認</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
+          <t>「FHA Food &amp; Hospitality Asia 2027」ジャパンパビリオンの設計・監理等</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
           <t>JETRO（日本貿易振興機構）</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
           <t>要（全省庁統一資格・役務の提供等）</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>新規【募集中】</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>https://www.jetro.go.jp/procurement/bid/ode/b086abd8177ce6da.html</t>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>https://www.jetro.go.jp/procurement/bid/afb/f2fc6a2a039f0ff2.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>○ 応募可（資格不要）</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>海外向けグリーンツーリズム推進事業セールスツール制作委託業務</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>大分県</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>https://www.pref.oita.jp/site/nyusatu-koubo/oita-greentourism.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>「FHA Food &amp; Hospitality Asia 2027」ジャパンパビリオンの設計・監理等</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>△ 統一資格の等級を要確認</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>「2027年ベオグラード国際博覧会」日本館 展示・施工等</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>JETRO（日本貿易振興機構）</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>要（全省庁統一資格・役務の提供等）</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>新規【募集中】</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>https://www.jetro.go.jp/procurement/bid/afb/f2fc6a2a039f0ff2.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>海外向けグリーンツーリズム推進事業セールスツール制作委託業務</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>大分県</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>不要</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>新規</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>https://www.pref.oita.jp/site/nyusatu-koubo/oita-greentourism.html</t>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>https://www.jetro.go.jp/procurement/bid/ode/3d8a541ddc5dccaa.html</t>
         </is>
       </c>
     </row>
@@ -1487,43 +1585,48 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>「2027年ベオグラード国際博覧会」日本館 展示・施工等</t>
+          <t>△ 統一資格の等級を要確認</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>JETRO（日本貿易振興機構）</t>
+          <t>スタートアップ向け広報イベントおよびアルムナイイベントの実施・運営等</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>JETRO（日本貿易振興機構）イノベーション部スタートアップ課</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>要（全省庁統一資格・役務の提供等）</t>
+          <t>非公開</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>新規【募集中】</t>
+          <t>要（全省庁統一資格 役務の提供等A/B/C）</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>https://www.jetro.go.jp/procurement/bid/ode/3d8a541ddc5dccaa.html</t>
+          <t>入札書等受領 9/14 11時。説明会9/7 13時（Teams・9/7 9時までに要事前申込）。**統一資格が間に合わない場合はJETRO独自の等級確認。申請期限9/8 17時・結果通知9/9 17時**</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>https://www.jetro.go.jp/procurement/bid/ivd/363416397290157f.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
@@ -1532,32 +1635,37 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>スタートアップ向け広報イベントおよびアルムナイイベントの実施・運営等</t>
+          <t>△ 要確認</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>JETRO（日本貿易振興機構）イノベーション部スタートアップ課</t>
+          <t>「FOODEX JAPAN2027」群馬県ブース全体装飾等設営業務公募型プロポーザルの実施について</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>非公開</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>要（全省庁統一資格 役務の提供等A/B/C）</t>
+          <t>300万円（上限・税込）</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>入札書等受領 9/14 11時。説明会9/7 13時（Teams・9/7 9時までに要事前申込）。**統一資格が間に合わない場合はJETRO独自の等級確認。申請期限9/8 17時・結果通知9/9 17時**</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>https://www.jetro.go.jp/procurement/bid/ivd/363416397290157f.html</t>
+          <t>新規（応募可）</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pref.gunma.jp/site/nyuusatsu/770814.html</t>
         </is>
       </c>
     </row>
@@ -1572,48 +1680,53 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>「FOODEX JAPAN2027」群馬県ブース全体装飾等設営業務公募型プロポーザルの実施について</t>
+          <t>× 等級不足（都はC）</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>令和8年度第39回全国健康福祉祭東京大会の開催を契機とした気運醸成事業実施委託</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>300万円（上限・税込）</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>非公開</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>新規（応募可）</t>
+          <t>要（東京都物品／115広告代理・受付等級A）</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>https://www.pref.gunma.jp/site/nyuusatsu/770814.html</t>
+          <t>**受付等級A。御社はC等級のため応募できない。**希望申請9/18 16時。ねんりんピック東京2028の第1号発注。等級Aが要るため、定期受付での等級向上が課題</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>https://www.e-procurement.metro.tokyo.lg.jp/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
@@ -1622,43 +1735,48 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>令和8年度第39回全国健康福祉祭東京大会の開催を契機とした気運醸成事業実施委託</t>
+          <t>△ 要確認</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>「RoboNext2026」静岡県ブースに係る設営等業務</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>非公開</t>
+          <t>静岡県産業振興財団</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>要（東京都物品／115広告代理・受付等級A）</t>
+          <t>2,080,000円（上限・税込）</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>**ねんりんピック東京2028の発注が出始めた第1号。**希望申請9/18 16時。東京都の名簿に未登載のため応募不可。等級Aが必要</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>https://www.e-procurement.metro.tokyo.lg.jp/</t>
+          <t>新規（応募可・9/25午前中必着）</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ric-shizuoka.or.jp/news_topics/news.php?id=174</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
@@ -1667,82 +1785,42 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>「RoboNext2026」静岡県ブースに係る設営等業務</t>
+          <t>○ 応募可（資格不要）</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>静岡県産業振興財団</t>
+          <t>小規模事業者持続化補助金＜共同・協業型＞第3回</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>2,080,000円（上限・税込）</t>
+          <t>中小企業庁</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>2000万-3000万</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>新規（応募可・9/25午前中必着）</t>
+          <t>不要</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>https://www.ric-shizuoka.or.jp/news_topics/news.php?id=174</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>小規模事業者持続化補助金＜共同・協業型＞第3回</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>中小企業庁</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>2000万-3000万</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>不要</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
           <t>新規（応募可・要GビズID）</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>https://r6.kyodokyogyohojokin.info/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I24"/>
+  <autoFilter ref="A1:J23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9821,7 +9899,7 @@
       </c>
       <c r="K130" s="9" t="inlineStr">
         <is>
-          <t>希望申請8/28 16時で締切。名簿未登載のため応募不可。**締切後は一覧から消える**</t>
+          <t>受付等級B。御社はC等級のため応募できない。8/28で締切済み</t>
         </is>
       </c>
       <c r="L130" s="9" t="inlineStr">
@@ -9883,7 +9961,7 @@
       </c>
       <c r="K131" s="9" t="inlineStr">
         <is>
-          <t>希望申請8/28 16時で締切。名簿未登載のため応募不可。**締切後は一覧から消える**</t>
+          <t>受付等級B。御社はC等級のため応募できない。8/28で締切済み</t>
         </is>
       </c>
       <c r="L131" s="9" t="inlineStr">
@@ -9945,7 +10023,7 @@
       </c>
       <c r="K132" s="9" t="inlineStr">
         <is>
-          <t>希望申請8/28 16時で締切。名簿未登載のため応募不可</t>
+          <t>受付等級C。**応募できたが8/28で締切済み**</t>
         </is>
       </c>
       <c r="L132" s="9" t="inlineStr">
@@ -10716,7 +10794,7 @@
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E145" s="9" t="inlineStr">
@@ -10751,7 +10829,7 @@
       </c>
       <c r="K145" s="9" t="inlineStr">
         <is>
-          <t>希望申請9/1 16時。東京都の名簿に未登載のため応募不可。開札9/17 9時40分</t>
+          <t>**受付等級C＝御社の現有資格で応募可。希望申請 9/1 16時（電子調達システムから）。**都立高校生と海外大学生の英語交流事業の企画・運営、会場手配、通訳者手配。履行〜令和9年1月29日。開札9/17 9時40分。教育庁総務部契約管財課 03-5320-6725</t>
         </is>
       </c>
       <c r="L145" s="9" t="inlineStr">
@@ -10813,7 +10891,7 @@
       </c>
       <c r="K146" s="9" t="inlineStr">
         <is>
-          <t>希望申請9/2 17時。東京都の競争入札参加有資格者名簿に未登載のため応募不可。開札9/16 9時35分</t>
+          <t>**受付等級B。御社はC等級のため応募できない。**希望申請9/2 17時。エコプロ2026の東京都ブース準備・運営。スタートアップ戦略推進本部</t>
         </is>
       </c>
       <c r="L146" s="9" t="inlineStr">
@@ -10875,7 +10953,7 @@
       </c>
       <c r="K147" s="9" t="inlineStr">
         <is>
-          <t>希望申請9/2 17時。東京都の名簿に未登載のため応募不可。開札9/16 9時35分</t>
+          <t>**受付等級B。御社はC等級のため応募できない。**希望申請9/2 17時</t>
         </is>
       </c>
       <c r="L147" s="9" t="inlineStr">
@@ -11061,7 +11139,7 @@
       </c>
       <c r="K150" s="9" t="inlineStr">
         <is>
-          <t>希望申請9/3 17時。東京都の名簿に未登載のため応募不可</t>
+          <t>**受付等級B。御社はC等級のため応募できない。**希望申請9/3 17時</t>
         </is>
       </c>
       <c r="L150" s="9" t="inlineStr">
@@ -11088,7 +11166,7 @@
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E151" s="9" t="inlineStr">
@@ -11123,7 +11201,7 @@
       </c>
       <c r="K151" s="9" t="inlineStr">
         <is>
-          <t>希望申請9/3 16時。**スクリプトの1ページ目問題を修正して初めて見えた案件。**名簿未登載のため応募不可</t>
+          <t>**受付等級B,C＝御社の現有資格で応募可。希望申請 9/3 16時。**イベント前日の設営と当日の運営。履行〜令和9年1月29日。開札9/28 10時。デジタルサービス局総務部企画計理課 03-5388-2085</t>
         </is>
       </c>
       <c r="L151" s="9" t="inlineStr">
@@ -11336,7 +11414,7 @@
       </c>
       <c r="D155" s="9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E155" s="9" t="inlineStr">
@@ -11371,7 +11449,7 @@
       </c>
       <c r="K155" s="9" t="inlineStr">
         <is>
-          <t>希望申請9/4 16時。2か年契約。名簿未登載のため応募不可</t>
+          <t>**受付等級A。御社はC等級のため応募できない。**希望申請9/4 16時</t>
         </is>
       </c>
       <c r="L155" s="9" t="inlineStr">
@@ -12452,7 +12530,7 @@
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E173" s="9" t="inlineStr">
@@ -12487,7 +12565,7 @@
       </c>
       <c r="K173" s="9" t="inlineStr">
         <is>
-          <t>**ねんりんピック東京2028の発注が出始めた第1号。**希望申請9/18 16時。東京都の名簿に未登載のため応募不可。等級Aが必要</t>
+          <t>**受付等級A。御社はC等級のため応募できない。**希望申請9/18 16時。ねんりんピック東京2028の第1号発注。等級Aが要るため、定期受付での等級向上が課題</t>
         </is>
       </c>
       <c r="L173" s="9" t="inlineStr">
@@ -18304,7 +18382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -18338,83 +18416,83 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>分母（業種フィルタなしの全案件名）</t>
+          <t>【資格】全省庁統一資格</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>9,247件 / 173組織</t>
+          <t>**D等級・取得済み**</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27 実測。巡回対象218組織</t>
+          <t>当面Dのまま。Dで届かない案件はコンソーシアムまたは再委託先として参加する</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>該当（3段ゲート通過）</t>
+          <t>【資格】東京都 競争入札参加資格</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>660件（S=66 / A=87 / B=507）</t>
+          <t>**C等級・取得済み**</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>該当率 7.1%</t>
+          <t>受付等級にCを含む案件のみ応募できる。等級を変えられるのは定期受付（2026-09-14〜10-30）のときだけ</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>台帳</t>
+          <t>【資格】東京都の営業種目</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>255件</t>
+          <t>**未確認**</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>当初100件から積み上げた</t>
+          <t>**120 催事関係業務が入っているかが分岐点。**入っていなければ催事案件に応募できない</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>要確認</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>補助金（全国）</t>
+          <t>分母（業種フィルタなしの全案件名）</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>9,247件 / 173組織</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>jGrants公開APIで構造化取得。ここに漏れはない</t>
+          <t>2026-08-27 実測。巡回対象218組織</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -18426,17 +18504,17 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>都道府県 本体</t>
+          <t>該当（3段ゲート通過）</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>47/47</t>
+          <t>660件（S=66 / A=87 / B=507）</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>2階層で並列巡回</t>
+          <t>該当率 7.1%</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -18448,83 +18526,83 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>都道府県 産業振興外郭団体</t>
+          <t>台帳</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>45/47</t>
+          <t>255件</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>長野・鹿児島のみ未特定</t>
+          <t>当初100件から積み上げた</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>政令市・中核市・東京23区</t>
+          <t>補助金（全国）</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>90/91</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>中野区のみ未特定</t>
+          <t>jGrants公開APIで構造化取得。ここに漏れはない</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>一般市町村（約1,700）</t>
+          <t>都道府県 本体</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>47/47</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>**最大の未踏領域。**検索で部分的に補完しているのみ</t>
+          <t>2階層で並列巡回</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>国の府省庁</t>
+          <t>都道府県 産業振興外郭団体</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>主要4省庁＋文化庁</t>
+          <t>45/47</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>文化庁・観光庁・経産省・内閣府の到達URLを確立</t>
+          <t>長野・鹿児島のみ未特定</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -18536,17 +18614,17 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>国の外郭団体</t>
+          <t>政令市・中核市・東京23区</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>17組織</t>
+          <t>90/91</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>CLAIR・JETRO・中小機構・国際交流基金・JNTO・VIPOほか</t>
+          <t>中野区のみ未特定</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -18558,181 +18636,247 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>東京都 電子調達システム</t>
+          <t>一般市町村（約1,700）</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>到達確立</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28 にPOST経路を確立。発注予定情報を隔日で取得</t>
+          <t>**最大の未踏領域。**検索で部分的に補完しているのみ</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>△</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>2027年国際園芸博覧会協会</t>
+          <t>国の府省庁</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>隔日監視</t>
+          <t>主要4省庁＋文化庁</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>直近2か月で委託等20件</t>
+          <t>文化庁・観光庁・経産省・内閣府の到達URLを確立</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>○</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>反復発注者6団体</t>
+          <t>国の外郭団体</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>隔日監視</t>
+          <t>17組織</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>年次サイクルを実測済み</t>
+          <t>CLAIR・JETRO・中小機構・国際交流基金・JNTO・VIPOほか</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>◎</t>
+          <t>○</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>持ち回り全国イベント</t>
+          <t>東京都 電子調達システム</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>12種を登録</t>
+          <t>到達確立</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>和牛全共・海づくり大会は一次資料で開催地確定</t>
+          <t>2026-08-28 にPOST経路を確立。発注予定情報を隔日で取得</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>調達ポータル p-portal</t>
+          <t>2027年国際園芸博覧会協会</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>到達不可</t>
+          <t>隔日監視</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>POSTがサーバ側の画面遷移検証で通らない。実害は小（省庁ページとJETROで重複取得）</t>
+          <t>直近2か月で委託等20件</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>◎</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>岐阜県・山梨県・えひめ産業振興財団</t>
+          <t>反復発注者6団体</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>到達不可</t>
+          <t>隔日監視</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>TLSは成立するがサーバが無応答で切断</t>
+          <t>年次サイクルを実測済み</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>◎</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>岡山県産業振興財団</t>
+          <t>持ち回り全国イベント</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>到達不可</t>
+          <t>12種を登録</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>HTTP 423 の人間確認画面</t>
+          <t>和牛全共・海づくり大会は一次資料で開催地確定</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>○</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
+          <t>調達ポータル p-portal</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>到達不可</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>POSTがサーバ側の画面遷移検証で通らない。実害は小（省庁ページとJETROで重複取得）</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>岐阜県・山梨県・えひめ産業振興財団</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>到達不可</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>TLSは成立するがサーバが無応答で切断</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>岡山県産業振興財団</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>到達不可</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>HTTP 423 の人間確認画面</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
           <t>東京都生活文化スポーツ局・VIPO</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>JSレンダリング</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>本文が静的HTMLに出ない。東京都は電子調達システムから取得できる</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D19"/>
+  <autoFilter ref="A1:D22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/lists/kobo_all_20260831.xlsx
+++ b/reports/lists/kobo_all_20260831.xlsx
@@ -955,12 +955,12 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>要（東京都物品／120催事関係業務・受付等級C）</t>
+          <t>要（東京都物品／120催事関係業務・受付等級C）**登録済み・等級一致を一次資料で確認**</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>**受付等級C＝御社の現有資格で応募可。希望申請 9/1 16時（電子調達システムから）。**都立高校生と海外大学生の英語交流事業の企画・運営、会場手配、通訳者手配。履行〜令和9年1月29日。開札9/17 9時40分。教育庁総務部契約管財課 03-5320-6725</t>
+          <t>**応募可。希望申請 9/1 16時（電子調達システムから）。**都立高校生と海外大学生の英語交流事業の企画・運営、会場手配、通訳者手配。履行〜令和9年1月29日。開札9/17 9:40。教育庁総務部契約管財課 03-5320-6725</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>**受付等級B。御社はC等級のため応募できない。**希望申請9/2 17時。エコプロ2026の東京都ブース準備・運営。スタートアップ戦略推進本部</t>
+          <t>**種目120は登録済みだが受付等級Bのため、C等級の当社は応募できない。**希望申請9/2 17時。エコプロ2026の東京都ブース準備・運営</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>**受付等級B。御社はC等級のため応募できない。**希望申請9/2 17時</t>
+          <t>**種目120は登録済みだが受付等級Bのため応募できない。**希望申請9/2 17時</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>**受付等級B。御社はC等級のため応募できない。**希望申請9/3 17時</t>
+          <t>**種目120は登録済みだが受付等級Bのため応募できない。**希望申請9/3 17時</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
@@ -1205,12 +1205,12 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>要（東京都物品／120催事関係業務・受付等級B,C）</t>
+          <t>要（東京都物品／120催事関係業務・受付等級B,C）**登録済み・等級一致を一次資料で確認**</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>**受付等級B,C＝御社の現有資格で応募可。希望申請 9/3 16時。**イベント前日の設営と当日の運営。履行〜令和9年1月29日。開札9/28 10時。デジタルサービス局総務部企画計理課 03-5388-2085</t>
+          <t>**応募可。希望申請 9/3 16時。**イベント前日の設営と当日の運営。履行〜令和9年1月29日。開札9/28 10:00。デジタルサービス局総務部企画計理課 03-5388-2085</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>**受付等級A。御社はC等級のため応募できない。**希望申請9/18 16時。ねんりんピック東京2028の第1号発注。等級Aが要るため、定期受付での等級向上が課題</t>
+          <t>**種目115は登録済みだが受付等級Aのため応募できない。**希望申請9/18 16時。ねんりんピック東京2028の第1号発注。**定期受付で等級を上げないと本体発注も同じ結果になる**</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="J145" s="9" t="inlineStr">
         <is>
-          <t>要（東京都物品／120催事関係業務・受付等級C）</t>
+          <t>要（東京都物品／120催事関係業務・受付等級C）**登録済み・等級一致を一次資料で確認**</t>
         </is>
       </c>
       <c r="K145" s="9" t="inlineStr">
         <is>
-          <t>**受付等級C＝御社の現有資格で応募可。希望申請 9/1 16時（電子調達システムから）。**都立高校生と海外大学生の英語交流事業の企画・運営、会場手配、通訳者手配。履行〜令和9年1月29日。開札9/17 9時40分。教育庁総務部契約管財課 03-5320-6725</t>
+          <t>**応募可。希望申請 9/1 16時（電子調達システムから）。**都立高校生と海外大学生の英語交流事業の企画・運営、会場手配、通訳者手配。履行〜令和9年1月29日。開札9/17 9:40。教育庁総務部契約管財課 03-5320-6725</t>
         </is>
       </c>
       <c r="L145" s="9" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K146" s="9" t="inlineStr">
         <is>
-          <t>**受付等級B。御社はC等級のため応募できない。**希望申請9/2 17時。エコプロ2026の東京都ブース準備・運営。スタートアップ戦略推進本部</t>
+          <t>**種目120は登録済みだが受付等級Bのため、C等級の当社は応募できない。**希望申請9/2 17時。エコプロ2026の東京都ブース準備・運営</t>
         </is>
       </c>
       <c r="L146" s="9" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="K147" s="9" t="inlineStr">
         <is>
-          <t>**受付等級B。御社はC等級のため応募できない。**希望申請9/2 17時</t>
+          <t>**種目120は登録済みだが受付等級Bのため応募できない。**希望申請9/2 17時</t>
         </is>
       </c>
       <c r="L147" s="9" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="K150" s="9" t="inlineStr">
         <is>
-          <t>**受付等級B。御社はC等級のため応募できない。**希望申請9/3 17時</t>
+          <t>**種目120は登録済みだが受付等級Bのため応募できない。**希望申請9/3 17時</t>
         </is>
       </c>
       <c r="L150" s="9" t="inlineStr">
@@ -11196,12 +11196,12 @@
       </c>
       <c r="J151" s="9" t="inlineStr">
         <is>
-          <t>要（東京都物品／120催事関係業務・受付等級B,C）</t>
+          <t>要（東京都物品／120催事関係業務・受付等級B,C）**登録済み・等級一致を一次資料で確認**</t>
         </is>
       </c>
       <c r="K151" s="9" t="inlineStr">
         <is>
-          <t>**受付等級B,C＝御社の現有資格で応募可。希望申請 9/3 16時。**イベント前日の設営と当日の運営。履行〜令和9年1月29日。開札9/28 10時。デジタルサービス局総務部企画計理課 03-5388-2085</t>
+          <t>**応募可。希望申請 9/3 16時。**イベント前日の設営と当日の運営。履行〜令和9年1月29日。開札9/28 10:00。デジタルサービス局総務部企画計理課 03-5388-2085</t>
         </is>
       </c>
       <c r="L151" s="9" t="inlineStr">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="K155" s="9" t="inlineStr">
         <is>
-          <t>**受付等級A。御社はC等級のため応募できない。**希望申請9/4 16時</t>
+          <t>**種目115は登録済みだが受付等級Aのため応募できない。**希望申請9/4 16時。2か年契約</t>
         </is>
       </c>
       <c r="L155" s="9" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="K173" s="9" t="inlineStr">
         <is>
-          <t>**受付等級A。御社はC等級のため応募できない。**希望申請9/18 16時。ねんりんピック東京2028の第1号発注。等級Aが要るため、定期受付での等級向上が課題</t>
+          <t>**種目115は登録済みだが受付等級Aのため応募できない。**希望申請9/18 16時。ねんりんピック東京2028の第1号発注。**定期受付で等級を上げないと本体発注も同じ結果になる**</t>
         </is>
       </c>
       <c r="L173" s="9" t="inlineStr">

--- a/reports/lists/kobo_all_20260831.xlsx
+++ b/reports/lists/kobo_all_20260831.xlsx
@@ -14,7 +14,7 @@
     <sheet name="4_巡回範囲と到達度" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_直近の申請候補'!$A$1:$J$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_直近の申請候補'!$A$1:$J$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2_全案件'!$A$1:$L$256</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3_未来（未公告）'!$A$1:$E$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4_巡回範囲と到達度'!$A$1:$D$22</definedName>
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -950,7 +950,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>非公開</t>
+          <t>【推定】約385万円／R7実績 落札3,850,000円（税込・大和田組）入札5社 350万〜685万（税抜）</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>非公開</t>
+          <t>【推定】約1,463万円／R7エコプロ版 落札14,630,000円 入札6社 1,330万〜3,190万（税抜）</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>非公開</t>
+          <t>【推定】約1,100万円／その2 落札11,440,000円・本体 10,706,300円・R7 10,716,200円</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>非公開</t>
+          <t>4,300千円（上限・税込）</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>非公開</t>
+          <t>【推定】約219万円／R7 落札2,194,500円 入札4社 199.5万〜560万（税抜）</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>非公開</t>
+          <t>【推定】約640万円／前身「Tokyo区市町村DXフェスタ」R7 落札6,431,700円 入札10社 585万〜889万（税抜）</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>21,945千円（税込）以内／R8年度 6,336千円・R9年度 15,609千円の2か年</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>「2027年ベオグラード国際博覧会」日本館 運営</t>
+          <t>「FHA Food &amp; Hospitality Asia 2027」ジャパンパビリオンの設計・監理等</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -1400,183 +1400,183 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>【推定】約180万円／FHA2026版 契約1,783,200円（アライズ）。BIOFACH2026 166.9万・Gulfood2026 217.4万・THAIFEX2026 180.3万</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>要（全省庁統一資格・役務の提供等）</t>
+          <t>要（統一資格 役務の提供等 **B・C・D等級**）→ **D等級の当社は直接応募できる**</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>新規【募集中】</t>
+          <t>**D等級で応募可。当社の統一資格でそのまま入札できる唯一のJETRO案件。**入札書等の受領期限 9/8、開札 9/10、説明会あり。履行〜2027年5月28日。農林水産食品部 事業推進課 FHAジャパンパビリオン事務局 03-3582-5546</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>https://www.jetro.go.jp/procurement/bid/ode/b086abd8177ce6da.html</t>
+          <t>https://www.jetro.go.jp/procurement/bid/afb/f2fc6a2a039f0ff2.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>○ 応募可（資格不要）</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>海外向けグリーンツーリズム推進事業セールスツール制作委託業務</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>大分県</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>https://www.pref.oita.jp/site/nyusatu-koubo/oita-greentourism.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>△ 統一資格の等級を要確認</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>「FHA Food &amp; Hospitality Asia 2027」ジャパンパビリオンの設計・監理等</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>JETRO（日本貿易振興機構）</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>要（全省庁統一資格・役務の提供等）</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>新規【募集中】</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>https://www.jetro.go.jp/procurement/bid/afb/f2fc6a2a039f0ff2.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>○ 応募可（資格不要）</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>海外向けグリーンツーリズム推進事業セールスツール制作委託業務</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>大分県</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>不要</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>新規</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>https://www.pref.oita.jp/site/nyusatu-koubo/oita-greentourism.html</t>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>△ 要確認</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>「FOODEX JAPAN2027」群馬県ブース全体装飾等設営業務公募型プロポーザルの実施について</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>群馬県</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>300万円（上限・税込）</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>新規（応募可）</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pref.gunma.jp/site/nyuusatsu/770814.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>△ 統一資格の等級を要確認</t>
+          <t>× 等級不足（都はC）</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>「2027年ベオグラード国際博覧会」日本館 展示・施工等</t>
+          <t>令和8年度第39回全国健康福祉祭東京大会の開催を契機とした気運醸成事業実施委託</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>JETRO（日本貿易振興機構）</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>【不明】同大会の「各種デザイン制作業務委託」は159.6万〜180万（税抜）</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>要（全省庁統一資格・役務の提供等）</t>
+          <t>要（東京都物品／115広告代理・受付等級A）</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>新規【募集中】</t>
+          <t>**種目115は登録済みだが受付等級Aのため応募できない。**希望申請9/18 16時。ねんりんピック東京2028の第1号発注。**定期受付で等級を上げないと本体発注も同じ結果になる**</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>https://www.jetro.go.jp/procurement/bid/ode/3d8a541ddc5dccaa.html</t>
+          <t>https://www.e-procurement.metro.tokyo.lg.jp/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
@@ -1585,48 +1585,48 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>△ 統一資格の等級を要確認</t>
+          <t>△ 要確認</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>スタートアップ向け広報イベントおよびアルムナイイベントの実施・運営等</t>
+          <t>「RoboNext2026」静岡県ブースに係る設営等業務</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>JETRO（日本貿易振興機構）イノベーション部スタートアップ課</t>
+          <t>静岡県産業振興財団</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>非公開</t>
+          <t>2,080,000円（上限・税込）</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>要（全省庁統一資格 役務の提供等A/B/C）</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>入札書等受領 9/14 11時。説明会9/7 13時（Teams・9/7 9時までに要事前申込）。**統一資格が間に合わない場合はJETRO独自の等級確認。申請期限9/8 17時・結果通知9/9 17時**</t>
+          <t>新規（応募可・9/25午前中必着）</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>https://www.jetro.go.jp/procurement/bid/ivd/363416397290157f.html</t>
+          <t>https://www.ric-shizuoka.or.jp/news_topics/news.php?id=174</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
@@ -1635,192 +1635,42 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>△ 要確認</t>
+          <t>○ 応募可（資格不要）</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>「FOODEX JAPAN2027」群馬県ブース全体装飾等設営業務公募型プロポーザルの実施について</t>
+          <t>小規模事業者持続化補助金＜共同・協業型＞第3回</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>中小企業庁</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>300万円（上限・税込）</t>
+          <t>2000万-3000万</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>不要</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>新規（応募可）</t>
+          <t>新規（応募可・要GビズID）</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>https://www.pref.gunma.jp/site/nyuusatsu/770814.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>× 等級不足（都はC）</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>令和8年度第39回全国健康福祉祭東京大会の開催を契機とした気運醸成事業実施委託</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>東京都</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>非公開</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>要（東京都物品／115広告代理・受付等級A）</t>
-        </is>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>**種目115は登録済みだが受付等級Aのため応募できない。**希望申請9/18 16時。ねんりんピック東京2028の第1号発注。**定期受付で等級を上げないと本体発注も同じ結果になる**</t>
-        </is>
-      </c>
-      <c r="J21" s="9" t="inlineStr">
-        <is>
-          <t>https://www.e-procurement.metro.tokyo.lg.jp/</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>△ 要確認</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>「RoboNext2026」静岡県ブースに係る設営等業務</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>静岡県産業振興財団</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>2,080,000円（上限・税込）</t>
-        </is>
-      </c>
-      <c r="H22" s="9" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>新規（応募可・9/25午前中必着）</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
-        <is>
-          <t>https://www.ric-shizuoka.or.jp/news_topics/news.php?id=174</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>○ 応募可（資格不要）</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>小規模事業者持続化補助金＜共同・協業型＞第3回</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>中小企業庁</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>2000万-3000万</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>不要</t>
-        </is>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>新規（応募可・要GビズID）</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="inlineStr">
-        <is>
           <t>https://r6.kyodokyogyohojokin.info/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J23"/>
+  <autoFilter ref="A1:J20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10814,7 +10664,7 @@
       </c>
       <c r="H145" s="9" t="inlineStr">
         <is>
-          <t>非公開</t>
+          <t>【推定】約385万円／R7実績 落札3,850,000円（税込・大和田組）入札5社 350万〜685万（税抜）</t>
         </is>
       </c>
       <c r="I145" s="9" t="inlineStr">
@@ -10876,7 +10726,7 @@
       </c>
       <c r="H146" s="9" t="inlineStr">
         <is>
-          <t>非公開</t>
+          <t>【推定】約1,463万円／R7エコプロ版 落札14,630,000円 入札6社 1,330万〜3,190万（税抜）</t>
         </is>
       </c>
       <c r="I146" s="9" t="inlineStr">
@@ -10938,7 +10788,7 @@
       </c>
       <c r="H147" s="9" t="inlineStr">
         <is>
-          <t>非公開</t>
+          <t>【推定】約1,100万円／その2 落札11,440,000円・本体 10,706,300円・R7 10,716,200円</t>
         </is>
       </c>
       <c r="I147" s="9" t="inlineStr">
@@ -11000,7 +10850,7 @@
       </c>
       <c r="H148" s="9" t="inlineStr">
         <is>
-          <t>非公開</t>
+          <t>4,300千円（上限・税込）</t>
         </is>
       </c>
       <c r="I148" s="9" t="inlineStr">
@@ -11124,7 +10974,7 @@
       </c>
       <c r="H150" s="9" t="inlineStr">
         <is>
-          <t>非公開</t>
+          <t>【推定】約219万円／R7 落札2,194,500円 入札4社 199.5万〜560万（税抜）</t>
         </is>
       </c>
       <c r="I150" s="9" t="inlineStr">
@@ -11186,7 +11036,7 @@
       </c>
       <c r="H151" s="9" t="inlineStr">
         <is>
-          <t>非公開</t>
+          <t>【推定】約640万円／前身「Tokyo区市町村DXフェスタ」R7 落札6,431,700円 入札10社 585万〜889万（税抜）</t>
         </is>
       </c>
       <c r="I151" s="9" t="inlineStr">
@@ -11310,7 +11160,7 @@
       </c>
       <c r="H153" s="9" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>21,945千円（税込）以内／R8年度 6,336千円・R9年度 15,609千円の2か年</t>
         </is>
       </c>
       <c r="I153" s="9" t="inlineStr">
@@ -11434,7 +11284,7 @@
       </c>
       <c r="H155" s="9" t="inlineStr">
         <is>
-          <t>非公開</t>
+          <t>【不明】2か年契約</t>
         </is>
       </c>
       <c r="I155" s="9" t="inlineStr">
@@ -11600,7 +11450,7 @@
       </c>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E158" s="9" t="inlineStr">
@@ -11620,7 +11470,7 @@
       </c>
       <c r="H158" s="9" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>【不明】新規案件のため過去契約なし</t>
         </is>
       </c>
       <c r="I158" s="9" t="inlineStr">
@@ -11630,12 +11480,12 @@
       </c>
       <c r="J158" s="9" t="inlineStr">
         <is>
-          <t>要（全省庁統一資格・役務の提供等）</t>
+          <t>要（統一資格 役務の提供等 A又はB等級）→ **D等級では不可**</t>
         </is>
       </c>
       <c r="K158" s="9" t="inlineStr">
         <is>
-          <t>新規【募集中】</t>
+          <t>**A又はB等級限定。D等級の当社は応募できない。**等級確認の申請期限は8/26で既に超過。共同企業体は可（構成員全法人が(1)〜(3)を満たすこと）</t>
         </is>
       </c>
       <c r="L158" s="9" t="inlineStr">
@@ -11682,7 +11532,7 @@
       </c>
       <c r="H159" s="9" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>【推定】約180万円／FHA2026版 契約1,783,200円（アライズ）。BIOFACH2026 166.9万・Gulfood2026 217.4万・THAIFEX2026 180.3万</t>
         </is>
       </c>
       <c r="I159" s="9" t="inlineStr">
@@ -11692,12 +11542,12 @@
       </c>
       <c r="J159" s="9" t="inlineStr">
         <is>
-          <t>要（全省庁統一資格・役務の提供等）</t>
+          <t>要（統一資格 役務の提供等 **B・C・D等級**）→ **D等級の当社は直接応募できる**</t>
         </is>
       </c>
       <c r="K159" s="9" t="inlineStr">
         <is>
-          <t>新規【募集中】</t>
+          <t>**D等級で応募可。当社の統一資格でそのまま入札できる唯一のJETRO案件。**入札書等の受領期限 9/8、開札 9/10、説明会あり。履行〜2027年5月28日。農林水産食品部 事業推進課 FHAジャパンパビリオン事務局 03-3582-5546</t>
         </is>
       </c>
       <c r="L159" s="9" t="inlineStr">
@@ -11910,7 +11760,7 @@
       </c>
       <c r="D163" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E163" s="9" t="inlineStr">
@@ -11930,7 +11780,7 @@
       </c>
       <c r="H163" s="9" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>【不明】新規案件のため過去契約なし</t>
         </is>
       </c>
       <c r="I163" s="9" t="inlineStr">
@@ -11940,12 +11790,12 @@
       </c>
       <c r="J163" s="9" t="inlineStr">
         <is>
-          <t>要（全省庁統一資格・役務の提供等）</t>
+          <t>要（統一資格 役務の提供等 A又はB等級）→ **D等級では不可**</t>
         </is>
       </c>
       <c r="K163" s="9" t="inlineStr">
         <is>
-          <t>新規【募集中】</t>
+          <t>**A又はB等級限定。D等級の当社は応募できない。**等級確認の申請期限は8/31 17時で超過。共同企業体は可</t>
         </is>
       </c>
       <c r="L163" s="9" t="inlineStr">
@@ -11972,7 +11822,7 @@
       </c>
       <c r="D164" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E164" s="9" t="inlineStr">
@@ -11992,7 +11842,7 @@
       </c>
       <c r="H164" s="9" t="inlineStr">
         <is>
-          <t>非公開</t>
+          <t>【不明】JETROのスタートアップ広報系は2,000万〜3.7億と幅が大きい（別案件の実績）</t>
         </is>
       </c>
       <c r="I164" s="9" t="inlineStr">
@@ -12002,12 +11852,12 @@
       </c>
       <c r="J164" s="9" t="inlineStr">
         <is>
-          <t>要（全省庁統一資格 役務の提供等A/B/C）</t>
+          <t>要（統一資格 役務の提供等 A・B・C等級）→ **D等級では不可**</t>
         </is>
       </c>
       <c r="K164" s="9" t="inlineStr">
         <is>
-          <t>入札書等受領 9/14 11時。説明会9/7 13時（Teams・9/7 9時までに要事前申込）。**統一資格が間に合わない場合はJETRO独自の等級確認。申請期限9/8 17時・結果通知9/9 17時**</t>
+          <t>**A・B・C等級限定。D等級の当社は応募できない。**等級確認（申請9/8 17時・通知9/9 17時）が使えるかは【不明】＝JETROへ要照会。追加要件としてPマーク／ISMS／IPA自己診断4.0以上のいずれかが必要</t>
         </is>
       </c>
       <c r="L164" s="9" t="inlineStr">
@@ -12550,7 +12400,7 @@
       </c>
       <c r="H173" s="9" t="inlineStr">
         <is>
-          <t>非公開</t>
+          <t>【不明】同大会の「各種デザイン制作業務委託」は159.6万〜180万（税抜）</t>
         </is>
       </c>
       <c r="I173" s="9" t="inlineStr">

--- a/reports/lists/kobo_all_20260831.xlsx
+++ b/reports/lists/kobo_all_20260831.xlsx
@@ -14,7 +14,7 @@
     <sheet name="4_巡回範囲と到達度" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_直近の申請候補'!$A$1:$J$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_直近の申請候補'!$A$1:$J$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2_全案件'!$A$1:$L$256</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3_未来（未公告）'!$A$1:$E$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4_巡回範囲と到達度'!$A$1:$D$22</definedName>
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -960,7 +960,7 @@
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>**応募可。希望申請 9/1 16時（電子調達システムから）。**都立高校生と海外大学生の英語交流事業の企画・運営、会場手配、通訳者手配。履行〜令和9年1月29日。開札9/17 9:40。教育庁総務部契約管財課 03-5320-6725</t>
+          <t>【生島様 2026-08-31：応募する】希望申請 9/1 16時。受付等級C・種目120で応募可。R7落札385万円（入札5社）。教育庁総務部契約管財課 03-5320-6725</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>**応募可。希望申請 9/3 16時。**イベント前日の設営と当日の運営。履行〜令和9年1月29日。開札9/28 10:00。デジタルサービス局総務部企画計理課 03-5388-2085</t>
+          <t>【生島様 2026-08-31：希望申請を出す】9/3 16時。受付等級B,C・種目120で応募可。前身のDXフェスタはR7落札643万円だが**入札10社の接戦**。デジタルサービス局 03-5388-2085</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>新規（応募可・参加意向申出9/7 17時／提案書9/29）</t>
+          <t>【生島様 2026-08-31：申請する】参加意向申出 9/7 17時必着（持参または書留）。単独応募可。上限1,430万円＋後続1.1〜4億円の単独随意契約。実績要件はア・イのいずれか一方。協会行催事課 045-307-2065</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -1320,357 +1320,107 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>× 等級不足（都はC）</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>令和8年度第39回全国健康福祉祭東京大会の開催を契機とした気運醸成事業実施委託</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>【不明】同大会の「各種デザイン制作業務委託」は159.6万〜180万（税抜）</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>要（東京都物品／115広告代理・受付等級A）</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>**種目115は登録済みだが受付等級Aのため応募できない。**希望申請9/18 16時。ねんりんピック東京2028の第1号発注。**定期受付で等級を上げないと本体発注も同じ結果になる**</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>https://www.e-procurement.metro.tokyo.lg.jp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>△ 要確認</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>集団出展ブース装飾委託業務【LIFE×DESIGN 2027】</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>公益財団法人わかやま産業振興財団</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>2,500,000円（上限・税込）</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>要（和歌山県 役務の提供等の入札参加資格）</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>新規（応募可・参加申込9/8 17時必着／提案書9/29）</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>https://yarukiouendan.or.jp/news/lifedesign_soushoku_2027/</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>△ 統一資格の等級を要確認</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>「FHA Food &amp; Hospitality Asia 2027」ジャパンパビリオンの設計・監理等</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>JETRO（日本貿易振興機構）</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>【推定】約180万円／FHA2026版 契約1,783,200円（アライズ）。BIOFACH2026 166.9万・Gulfood2026 217.4万・THAIFEX2026 180.3万</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>要（統一資格 役務の提供等 **B・C・D等級**）→ **D等級の当社は直接応募できる**</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>**D等級で応募可。当社の統一資格でそのまま入札できる唯一のJETRO案件。**入札書等の受領期限 9/8、開札 9/10、説明会あり。履行〜2027年5月28日。農林水産食品部 事業推進課 FHAジャパンパビリオン事務局 03-3582-5546</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>https://www.jetro.go.jp/procurement/bid/afb/f2fc6a2a039f0ff2.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>○ 応募可（資格不要）</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>海外向けグリーンツーリズム推進事業セールスツール制作委託業務</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>大分県</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>小規模事業者持続化補助金＜共同・協業型＞第3回</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>中小企業庁</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>上限3,000万円（参画10者以上）／2,000万円（5〜9者）・公募要領P.8明示</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>新規</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>https://www.pref.oita.jp/site/nyusatu-koubo/oita-greentourism.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>△ 要確認</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>「FOODEX JAPAN2027」群馬県ブース全体装飾等設営業務公募型プロポーザルの実施について</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>群馬県</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>300万円（上限・税込）</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>新規（応募可）</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="inlineStr">
-        <is>
-          <t>https://www.pref.gunma.jp/site/nyuusatsu/770814.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>× 等級不足（都はC）</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>令和8年度第39回全国健康福祉祭東京大会の開催を契機とした気運醸成事業実施委託</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>東京都</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>【不明】同大会の「各種デザイン制作業務委託」は159.6万〜180万（税抜）</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>要（東京都物品／115広告代理・受付等級A）</t>
-        </is>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>**種目115は登録済みだが受付等級Aのため応募できない。**希望申請9/18 16時。ねんりんピック東京2028の第1号発注。**定期受付で等級を上げないと本体発注も同じ結果になる**</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="inlineStr">
-        <is>
-          <t>https://www.e-procurement.metro.tokyo.lg.jp/</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>△ 要確認</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>「RoboNext2026」静岡県ブースに係る設営等業務</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>静岡県産業振興財団</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>2,080,000円（上限・税込）</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>新規（応募可・9/25午前中必着）</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="inlineStr">
-        <is>
-          <t>https://www.ric-shizuoka.or.jp/news_topics/news.php?id=174</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>○ 応募可（資格不要）</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>小規模事業者持続化補助金＜共同・協業型＞第3回</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>中小企業庁</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>2000万-3000万</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>不要</t>
-        </is>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>新規（応募可・要GビズID）</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>【生島様 2026-08-31：検討中。企画を立てて申請したい】9/30 17:00 Jグランツ電子申請。**GビズIDプライム必須（未取得なら数週間・8/28からオンライン申請に不具合、9月上旬解消予定）**。参画事業者10者以上=3,000万円／5〜9者=2,000万円。「過去と同様の事業は対象外」は**審査視点が「過去の類似事業と比べて発展性はあるか」なので外せる**。企画案は workflow/jizokuka_kyodo_r8_3.md</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>https://r6.kyodokyogyohojokin.info/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J20"/>
+  <autoFilter ref="A1:J15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10679,7 +10429,7 @@
       </c>
       <c r="K145" s="9" t="inlineStr">
         <is>
-          <t>**応募可。希望申請 9/1 16時（電子調達システムから）。**都立高校生と海外大学生の英語交流事業の企画・運営、会場手配、通訳者手配。履行〜令和9年1月29日。開札9/17 9:40。教育庁総務部契約管財課 03-5320-6725</t>
+          <t>【生島様 2026-08-31：応募する】希望申請 9/1 16時。受付等級C・種目120で応募可。R7落札385万円（入札5社）。教育庁総務部契約管財課 03-5320-6725</t>
         </is>
       </c>
       <c r="L145" s="9" t="inlineStr">
@@ -10927,7 +10677,7 @@
       </c>
       <c r="K149" s="9" t="inlineStr">
         <is>
-          <t>参加意向申出 9/3 正午必着（郵送または持参のみ・電子不可）。実績要件は「共同企業体として有していればよい」と要領に明記。実績を持つ企業とJVを組めば応募可。単独では不可</t>
+          <t>【生島様 2026-08-31：見送り】単独応募不可。JVの相手を2日で探すのは現実的でない。**実績要件は「共同企業体として有していればよい」と要領に明記されており、協会の次の大型案件では組み方次第で入れる**</t>
         </is>
       </c>
       <c r="L149" s="9" t="inlineStr">
@@ -11051,7 +10801,7 @@
       </c>
       <c r="K151" s="9" t="inlineStr">
         <is>
-          <t>**応募可。希望申請 9/3 16時。**イベント前日の設営と当日の運営。履行〜令和9年1月29日。開札9/28 10:00。デジタルサービス局総務部企画計理課 03-5388-2085</t>
+          <t>【生島様 2026-08-31：希望申請を出す】9/3 16時。受付等級B,C・種目120で応募可。前身のDXフェスタはR7落札643万円だが**入札10社の接戦**。デジタルサービス局 03-5388-2085</t>
         </is>
       </c>
       <c r="L151" s="9" t="inlineStr">
@@ -11361,7 +11111,7 @@
       </c>
       <c r="K156" s="9" t="inlineStr">
         <is>
-          <t>新規（応募可・参加意向申出9/7 17時／提案書9/29）</t>
+          <t>【生島様 2026-08-31：申請する】参加意向申出 9/7 17時必着（持参または書留）。単独応募可。上限1,430万円＋後続1.1〜4億円の単独随意契約。実績要件はア・イのいずれか一方。協会行催事課 045-307-2065</t>
         </is>
       </c>
       <c r="L156" s="9" t="inlineStr">
@@ -11388,7 +11138,7 @@
       </c>
       <c r="D157" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E157" s="9" t="inlineStr">
@@ -11423,7 +11173,7 @@
       </c>
       <c r="K157" s="9" t="inlineStr">
         <is>
-          <t>新規（応募可・参加申込9/8 17時必着／提案書9/29）</t>
+          <t>【生島様 2026-08-31：見送り】**施工会社が取る可能性が高い。**運営・総合プロデュース要素がない。規模感が大きいか、運営・総合支援を含めば有利。次年度に条件が変われば拾い直す</t>
         </is>
       </c>
       <c r="L157" s="9" t="inlineStr">
@@ -11512,7 +11262,7 @@
       </c>
       <c r="D159" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E159" s="9" t="inlineStr">
@@ -11547,7 +11297,7 @@
       </c>
       <c r="K159" s="9" t="inlineStr">
         <is>
-          <t>**D等級で応募可。当社の統一資格でそのまま入札できる唯一のJETRO案件。**入札書等の受領期限 9/8、開札 9/10、説明会あり。履行〜2027年5月28日。農林水産食品部 事業推進課 FHAジャパンパビリオン事務局 03-3582-5546</t>
+          <t>【生島様 2026-08-31：見送り】D等級で応募できるが、約180万円と小規模かつ既存業者（アライズ）が4件中3件を取っている</t>
         </is>
       </c>
       <c r="L159" s="9" t="inlineStr">
@@ -11698,7 +11448,7 @@
       </c>
       <c r="D162" s="9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E162" s="9" t="inlineStr">
@@ -11733,7 +11483,7 @@
       </c>
       <c r="K162" s="9" t="inlineStr">
         <is>
-          <t>新規</t>
+          <t>【生島様 2026-08-31：見送り】制作単体のため</t>
         </is>
       </c>
       <c r="L162" s="9" t="inlineStr">
@@ -11857,7 +11607,7 @@
       </c>
       <c r="K164" s="9" t="inlineStr">
         <is>
-          <t>**A・B・C等級限定。D等級の当社は応募できない。**等級確認（申請9/8 17時・通知9/9 17時）が使えるかは【不明】＝JETROへ要照会。追加要件としてPマーク／ISMS／IPA自己診断4.0以上のいずれかが必要</t>
+          <t>【生島様 2026-08-31：見送り】統一資格A・B・C限定でD等級では不可</t>
         </is>
       </c>
       <c r="L164" s="9" t="inlineStr">
@@ -12008,7 +11758,7 @@
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E167" s="9" t="inlineStr">
@@ -12043,7 +11793,7 @@
       </c>
       <c r="K167" s="9" t="inlineStr">
         <is>
-          <t>新規（応募可）</t>
+          <t>【生島様 2026-08-31：見送り】**施工会社向け。海外であれば当社のノウハウが生きる。**次年度に海外案件として出れば拾う</t>
         </is>
       </c>
       <c r="L167" s="9" t="inlineStr">
@@ -12504,7 +12254,7 @@
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E175" s="9" t="inlineStr">
@@ -12539,7 +12289,7 @@
       </c>
       <c r="K175" s="9" t="inlineStr">
         <is>
-          <t>新規（応募可・9/25午前中必着）</t>
+          <t>【生島様 2026-08-31：見送り】施工単体のため。反復発注者として監視は継続</t>
         </is>
       </c>
       <c r="L175" s="9" t="inlineStr">
@@ -12586,7 +12336,7 @@
       </c>
       <c r="H176" s="9" t="inlineStr">
         <is>
-          <t>2000万-3000万</t>
+          <t>上限3,000万円（参画10者以上）／2,000万円（5〜9者）・公募要領P.8明示</t>
         </is>
       </c>
       <c r="I176" s="9" t="inlineStr">
@@ -12601,7 +12351,7 @@
       </c>
       <c r="K176" s="9" t="inlineStr">
         <is>
-          <t>新規（応募可・要GビズID）</t>
+          <t>【生島様 2026-08-31：検討中。企画を立てて申請したい】9/30 17:00 Jグランツ電子申請。**GビズIDプライム必須（未取得なら数週間・8/28からオンライン申請に不具合、9月上旬解消予定）**。参画事業者10者以上=3,000万円／5〜9者=2,000万円。「過去と同様の事業は対象外」は**審査視点が「過去の類似事業と比べて発展性はあるか」なので外せる**。企画案は workflow/jizokuka_kyodo_r8_3.md</t>
         </is>
       </c>
       <c r="L176" s="9" t="inlineStr">
